--- a/InputData/trans/BMRESP/BAU Min Req EV Sales Perc.xlsx
+++ b/InputData/trans/BMRESP/BAU Min Req EV Sales Perc.xlsx
@@ -1,22 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\trans\BMRESP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/BMRESP/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969FFE62-E574-A041-AD1E-5CA6510DCD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="23955" windowHeight="12090"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BMRESP-passenger" sheetId="2" r:id="rId2"/>
     <sheet name="BMRESP-freight" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -65,7 +79,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -127,9 +141,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -167,9 +181,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -204,7 +218,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -239,7 +253,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -412,16 +426,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -429,17 +443,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -451,17 +465,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AJ7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BD7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.265625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:56" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -570,8 +584,68 @@
       <c r="AJ1">
         <v>2050</v>
       </c>
+      <c r="AK1">
+        <v>2051</v>
+      </c>
+      <c r="AL1">
+        <v>2052</v>
+      </c>
+      <c r="AM1">
+        <v>2053</v>
+      </c>
+      <c r="AN1">
+        <v>2054</v>
+      </c>
+      <c r="AO1">
+        <v>2055</v>
+      </c>
+      <c r="AP1">
+        <v>2056</v>
+      </c>
+      <c r="AQ1">
+        <v>2057</v>
+      </c>
+      <c r="AR1">
+        <v>2058</v>
+      </c>
+      <c r="AS1">
+        <v>2059</v>
+      </c>
+      <c r="AT1">
+        <v>2060</v>
+      </c>
+      <c r="AU1">
+        <v>2061</v>
+      </c>
+      <c r="AV1">
+        <v>2062</v>
+      </c>
+      <c r="AW1">
+        <v>2063</v>
+      </c>
+      <c r="AX1">
+        <v>2064</v>
+      </c>
+      <c r="AY1">
+        <v>2065</v>
+      </c>
+      <c r="AZ1">
+        <v>2066</v>
+      </c>
+      <c r="BA1">
+        <v>2067</v>
+      </c>
+      <c r="BB1">
+        <v>2068</v>
+      </c>
+      <c r="BC1">
+        <v>2069</v>
+      </c>
+      <c r="BD1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -680,8 +754,88 @@
       <c r="AJ2">
         <v>0</v>
       </c>
+      <c r="AK2">
+        <f>AJ2</f>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" ref="AL2:BD7" si="0">AK2</f>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -790,8 +944,88 @@
       <c r="AJ3">
         <v>0</v>
       </c>
+      <c r="AK3">
+        <f t="shared" ref="AK3:AZ7" si="1">AJ3</f>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -900,8 +1134,88 @@
       <c r="AJ4">
         <v>0</v>
       </c>
+      <c r="AK4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1010,8 +1324,88 @@
       <c r="AJ5">
         <v>0</v>
       </c>
+      <c r="AK5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1120,8 +1514,88 @@
       <c r="AJ6">
         <v>0</v>
       </c>
+      <c r="AK6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1228,6 +1702,86 @@
         <v>0</v>
       </c>
       <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1237,17 +1791,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AJ7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BD7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.265625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:56" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -1356,8 +1910,68 @@
       <c r="AJ1">
         <v>2050</v>
       </c>
+      <c r="AK1">
+        <v>2051</v>
+      </c>
+      <c r="AL1">
+        <v>2052</v>
+      </c>
+      <c r="AM1">
+        <v>2053</v>
+      </c>
+      <c r="AN1">
+        <v>2054</v>
+      </c>
+      <c r="AO1">
+        <v>2055</v>
+      </c>
+      <c r="AP1">
+        <v>2056</v>
+      </c>
+      <c r="AQ1">
+        <v>2057</v>
+      </c>
+      <c r="AR1">
+        <v>2058</v>
+      </c>
+      <c r="AS1">
+        <v>2059</v>
+      </c>
+      <c r="AT1">
+        <v>2060</v>
+      </c>
+      <c r="AU1">
+        <v>2061</v>
+      </c>
+      <c r="AV1">
+        <v>2062</v>
+      </c>
+      <c r="AW1">
+        <v>2063</v>
+      </c>
+      <c r="AX1">
+        <v>2064</v>
+      </c>
+      <c r="AY1">
+        <v>2065</v>
+      </c>
+      <c r="AZ1">
+        <v>2066</v>
+      </c>
+      <c r="BA1">
+        <v>2067</v>
+      </c>
+      <c r="BB1">
+        <v>2068</v>
+      </c>
+      <c r="BC1">
+        <v>2069</v>
+      </c>
+      <c r="BD1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1466,8 +2080,88 @@
       <c r="AJ2">
         <v>0</v>
       </c>
+      <c r="AK2">
+        <f>AJ2</f>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" ref="AL2:BD7" si="0">AK2</f>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1576,8 +2270,88 @@
       <c r="AJ3">
         <v>0</v>
       </c>
+      <c r="AK3">
+        <f t="shared" ref="AK3:AZ7" si="1">AJ3</f>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1686,8 +2460,88 @@
       <c r="AJ4">
         <v>0</v>
       </c>
+      <c r="AK4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1796,8 +2650,88 @@
       <c r="AJ5">
         <v>0</v>
       </c>
+      <c r="AK5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1906,8 +2840,88 @@
       <c r="AJ6">
         <v>0</v>
       </c>
+      <c r="AK6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2014,6 +3028,86 @@
         <v>0</v>
       </c>
       <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
